--- a/data/trans_dic/IP08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,47</t>
+          <t>5,56; 14,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,12</t>
+          <t>3,63; 12,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 11,99</t>
+          <t>2,79; 12,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 16,5</t>
+          <t>6,26; 15,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 17,84</t>
+          <t>6,91; 17,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 13,98</t>
+          <t>4,51; 14,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,16</t>
+          <t>4,2; 13,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,11</t>
+          <t>6,31; 15,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,58</t>
+          <t>7,37; 14,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,65</t>
+          <t>4,96; 11,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,97</t>
+          <t>4,51; 10,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,95</t>
+          <t>7,24; 13,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 14,75</t>
+          <t>4,52; 15,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 14,1</t>
+          <t>5,0; 14,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,53</t>
+          <t>0,6; 5,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,03</t>
+          <t>4,56; 14,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 16,05</t>
+          <t>5,97; 16,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,4</t>
+          <t>4,76; 13,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 12,5</t>
+          <t>4,36; 12,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 18,45</t>
+          <t>6,6; 19,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,76</t>
+          <t>6,41; 13,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,71</t>
+          <t>5,67; 12,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,87</t>
+          <t>2,85; 7,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 14,61</t>
+          <t>6,48; 14,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,3</t>
+          <t>2,44; 11,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 15,27</t>
+          <t>4,87; 15,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 12,28</t>
+          <t>1,92; 12,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,9</t>
+          <t>1,56; 12,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 20,39</t>
+          <t>8,73; 20,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 21,4</t>
+          <t>8,7; 21,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,42</t>
+          <t>3,37; 13,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 21,74</t>
+          <t>6,25; 21,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 14,69</t>
+          <t>7,28; 15,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 16,3</t>
+          <t>8,04; 16,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,88</t>
+          <t>3,93; 11,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,39</t>
+          <t>5,51; 14,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 12,02</t>
+          <t>5,9; 12,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 21,51</t>
+          <t>12,61; 21,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,9</t>
+          <t>5,04; 11,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 20,55</t>
+          <t>6,76; 20,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,01</t>
+          <t>6,91; 13,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 21,59</t>
+          <t>13,47; 21,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,14</t>
+          <t>3,1; 8,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,89</t>
+          <t>10,62; 19,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,52</t>
+          <t>7,09; 11,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 20,1</t>
+          <t>14,1; 20,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,82</t>
+          <t>4,79; 8,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 17,61</t>
+          <t>9,74; 17,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,85</t>
+          <t>4,6; 13,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 16,51</t>
+          <t>7,88; 16,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,37</t>
+          <t>5,98; 14,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 16,63</t>
+          <t>6,69; 16,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,27</t>
+          <t>8,34; 17,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,1</t>
+          <t>11,77; 22,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 11,57</t>
+          <t>3,81; 11,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 39,63</t>
+          <t>8,81; 36,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 14,66</t>
+          <t>7,81; 14,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,12; 17,67</t>
+          <t>10,94; 18,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,21</t>
+          <t>6,15; 11,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 27,31</t>
+          <t>9,49; 28,25</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 13,17</t>
+          <t>3,08; 13,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 17,55</t>
+          <t>4,04; 17,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,9</t>
+          <t>1,24; 12,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 12,34</t>
+          <t>2,52; 13,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,37</t>
+          <t>6,26; 18,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,89</t>
+          <t>4,98; 15,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,94; 17,84</t>
+          <t>5,4; 18,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 15,2</t>
+          <t>3,77; 15,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 13,41</t>
+          <t>5,71; 13,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 14,07</t>
+          <t>5,72; 14,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 12,7</t>
+          <t>4,43; 12,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 11,37</t>
+          <t>4,03; 11,64</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,22</t>
+          <t>6,57; 10,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,04</t>
+          <t>9,87; 13,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,47</t>
+          <t>5,2; 8,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,76</t>
+          <t>7,76; 12,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,53</t>
+          <t>9,48; 13,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 15,71</t>
+          <t>11,64; 15,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,82</t>
+          <t>5,58; 8,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,71; 17,72</t>
+          <t>10,49; 17,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 11,35</t>
+          <t>8,6; 11,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 14,33</t>
+          <t>11,37; 14,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,03</t>
+          <t>5,76; 8,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,99</t>
+          <t>9,5; 14,21</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9789</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6802</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10623</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11474</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7494</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7476</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14264</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14296</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12834</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24888</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5800; 15447</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3263; 11617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2307; 10195</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6537; 16668</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6741; 16876</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4048; 12809</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4160; 13141</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8636; 21590</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14879; 29139</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8904; 20508</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8199; 19940</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>17468; 33256</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8531</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11242</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16392</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16780</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11098</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19443</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3949; 13653</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4662; 13481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>635; 6003</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4320; 13409</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5137; 13835</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4606; 13419</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4918; 14140</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6311; 18171</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11114; 23703</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10768; 23757</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6236; 17151</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12333; 26782</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8182</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13871</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12145</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17714</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20327</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9067</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10329</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1644; 7935</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4197; 13511</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1188; 7610</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>801; 6371</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8668; 20625</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7557; 18492</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2540; 10412</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3992; 13556</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12140; 25316</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13911; 28246</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5391; 15328</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6352; 16892</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34455</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16936</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25055</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39012</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10953</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>31228</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>37434</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73467</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27889</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>56283</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11851; 25233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25896; 43546</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11230; 24747</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14746; 44117</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13962; 28130</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>30731; 49560</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6479; 16815</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>23180; 42637</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>28539; 47753</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>61111; 87079</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>20703; 37567</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>42506; 76109</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8749</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17368</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13749</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13020</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23614</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9909</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>26496</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>24931</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40982</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>39515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4786; 14155</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11750; 24921</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8144; 19651</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7991; 19669</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10616; 22869</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16605; 31919</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5432; 15768</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14145; 57838</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>18080; 33117</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31751; 52254</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17144; 33034</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>26591; 79107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2895</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7008</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7150</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>13220</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>11944</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9729</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2309; 9786</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2177; 9422</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>746; 7381</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1735; 9000</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4530; 13282</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3686; 11575</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3666; 12750</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2716; 11102</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8406; 20225</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7318; 18126</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5681; 16287</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5685; 16402</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>52790</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>80218</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>44828</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>63548</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>78164</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97578</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>49764</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>96639</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>130953</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>177796</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>94592</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>160187</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>41958; 63891</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>66931; 94473</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>34795; 55623</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>50974; 83798</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>64880; 91946</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>83393; 112919</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>39466; 62714</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>78411; 128649</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>113794; 148427</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>158541; 198974</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>79243; 111218</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>133324; 199520</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,8</t>
+          <t>5,3; 14,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 12,92</t>
+          <t>3,79; 13,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,34</t>
+          <t>3,34; 12,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 15,96</t>
+          <t>5,74; 15,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 17,3</t>
+          <t>7,38; 17,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 14,27</t>
+          <t>4,43; 13,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 13,26</t>
+          <t>4,08; 12,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,77</t>
+          <t>6,3; 16,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,43</t>
+          <t>7,75; 14,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,41</t>
+          <t>5,24; 11,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,97</t>
+          <t>4,32; 10,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 13,78</t>
+          <t>7,34; 13,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,62</t>
+          <t>4,99; 15,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 14,45</t>
+          <t>4,72; 15,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,68</t>
+          <t>0,6; 5,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,16</t>
+          <t>4,74; 14,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 16,09</t>
+          <t>5,81; 16,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,87</t>
+          <t>4,72; 14,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,54</t>
+          <t>4,18; 12,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 19,01</t>
+          <t>6,94; 19,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,67</t>
+          <t>6,38; 13,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,5</t>
+          <t>5,85; 12,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,85</t>
+          <t>3,05; 7,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,08</t>
+          <t>6,81; 14,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,77</t>
+          <t>2,0; 11,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 15,68</t>
+          <t>5,12; 15,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 12,31</t>
+          <t>2,03; 12,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 12,39</t>
+          <t>1,55; 12,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 20,76</t>
+          <t>8,65; 19,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 21,28</t>
+          <t>8,66; 20,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 13,8</t>
+          <t>3,87; 13,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,23</t>
+          <t>5,81; 21,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,18</t>
+          <t>7,07; 15,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,32</t>
+          <t>8,17; 16,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 11,17</t>
+          <t>3,9; 10,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 14,65</t>
+          <t>4,89; 14,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,57</t>
+          <t>5,85; 12,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 21,2</t>
+          <t>12,81; 21,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,11</t>
+          <t>5,09; 10,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 20,24</t>
+          <t>7,3; 20,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,92</t>
+          <t>6,9; 13,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 21,73</t>
+          <t>12,96; 21,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,04</t>
+          <t>3,0; 8,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 19,53</t>
+          <t>10,43; 19,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,86</t>
+          <t>7,1; 11,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,09</t>
+          <t>14,38; 20,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,7</t>
+          <t>4,74; 8,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,45</t>
+          <t>9,74; 17,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,59</t>
+          <t>4,5; 13,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 16,71</t>
+          <t>7,84; 16,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,43</t>
+          <t>6,57; 15,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 16,47</t>
+          <t>6,83; 16,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,97</t>
+          <t>8,51; 18,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 22,63</t>
+          <t>11,88; 22,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,07</t>
+          <t>3,64; 10,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 36,01</t>
+          <t>8,46; 35,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 14,31</t>
+          <t>7,88; 14,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 18,0</t>
+          <t>11,22; 18,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,86</t>
+          <t>5,82; 11,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 28,25</t>
+          <t>9,47; 26,96</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,07</t>
+          <t>2,88; 13,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 17,48</t>
+          <t>3,99; 18,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,24</t>
+          <t>1,28; 11,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,06</t>
+          <t>2,28; 12,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 18,35</t>
+          <t>5,54; 18,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,63</t>
+          <t>4,92; 16,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 18,8</t>
+          <t>5,38; 18,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 15,42</t>
+          <t>3,7; 14,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,73</t>
+          <t>5,6; 13,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 14,17</t>
+          <t>5,44; 14,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 12,71</t>
+          <t>4,65; 12,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,64</t>
+          <t>3,92; 11,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,0</t>
+          <t>6,62; 10,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,94</t>
+          <t>9,81; 13,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,31</t>
+          <t>5,37; 8,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,76</t>
+          <t>7,58; 12,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,43</t>
+          <t>9,4; 13,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,76</t>
+          <t>11,46; 15,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,87</t>
+          <t>5,66; 8,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 17,22</t>
+          <t>10,48; 18,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,22</t>
+          <t>8,66; 11,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,27</t>
+          <t>11,37; 14,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,08</t>
+          <t>5,84; 7,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,21</t>
+          <t>9,7; 14,42</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5800; 15447</t>
+          <t>5531; 14749</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3263; 11617</t>
+          <t>3412; 12152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2307; 10195</t>
+          <t>2756; 10546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6537; 16668</t>
+          <t>5992; 15800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6741; 16876</t>
+          <t>7203; 17454</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4048; 12809</t>
+          <t>3976; 12432</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4160; 13141</t>
+          <t>4042; 12346</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8636; 21590</t>
+          <t>8625; 22146</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14879; 29139</t>
+          <t>15645; 30004</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8904; 20508</t>
+          <t>9410; 21118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8199; 19940</t>
+          <t>7857; 19366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17468; 33256</t>
+          <t>17725; 33521</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3949; 13653</t>
+          <t>4360; 13601</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4662; 13481</t>
+          <t>4403; 14165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635; 6003</t>
+          <t>635; 5906</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4320; 13409</t>
+          <t>4485; 14077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5137; 13835</t>
+          <t>4998; 14127</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4606; 13419</t>
+          <t>4569; 13598</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4918; 14140</t>
+          <t>4710; 14041</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6311; 18171</t>
+          <t>6637; 18873</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11114; 23703</t>
+          <t>11061; 23289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10768; 23757</t>
+          <t>11118; 24042</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6236; 17151</t>
+          <t>6657; 17239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12333; 26782</t>
+          <t>12964; 28217</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1644; 7935</t>
+          <t>1350; 7905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4197; 13511</t>
+          <t>4415; 13687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1188; 7610</t>
+          <t>1255; 7493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>801; 6371</t>
+          <t>796; 6336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8668; 20625</t>
+          <t>8590; 19481</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7557; 18492</t>
+          <t>7528; 18214</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2540; 10412</t>
+          <t>2916; 10500</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3992; 13556</t>
+          <t>3710; 13500</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12140; 25316</t>
+          <t>11785; 25758</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13911; 28246</t>
+          <t>14138; 28005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5391; 15328</t>
+          <t>5349; 14937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6352; 16892</t>
+          <t>5634; 16542</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11851; 25233</t>
+          <t>11742; 24187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25896; 43546</t>
+          <t>26299; 43988</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11230; 24747</t>
+          <t>11326; 24105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14746; 44117</t>
+          <t>15907; 44987</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13962; 28130</t>
+          <t>13951; 27509</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30731; 49560</t>
+          <t>29557; 49105</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6479; 16815</t>
+          <t>6279; 16989</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23180; 42637</t>
+          <t>22768; 42617</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28539; 47753</t>
+          <t>28617; 47927</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61111; 87079</t>
+          <t>62334; 87211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20703; 37567</t>
+          <t>20484; 37092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42506; 76109</t>
+          <t>42477; 77772</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4786; 14155</t>
+          <t>4689; 14449</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11750; 24921</t>
+          <t>11697; 24033</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8144; 19651</t>
+          <t>8951; 20851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7991; 19669</t>
+          <t>8162; 19538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10616; 22869</t>
+          <t>10833; 23212</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16605; 31919</t>
+          <t>16755; 31091</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5432; 15768</t>
+          <t>5190; 15648</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14145; 57838</t>
+          <t>13582; 57404</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18080; 33117</t>
+          <t>18227; 33179</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31751; 52254</t>
+          <t>32556; 52407</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17144; 33034</t>
+          <t>16201; 32158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26591; 79107</t>
+          <t>26509; 75492</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2309; 9786</t>
+          <t>2159; 9868</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2177; 9422</t>
+          <t>2153; 9728</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>746; 7381</t>
+          <t>770; 6637</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1735; 9000</t>
+          <t>1568; 8593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4530; 13282</t>
+          <t>4014; 13283</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3686; 11575</t>
+          <t>3646; 12372</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3666; 12750</t>
+          <t>3649; 12762</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2716; 11102</t>
+          <t>2661; 10641</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8406; 20225</t>
+          <t>8247; 19969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7318; 18126</t>
+          <t>6954; 17981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5681; 16287</t>
+          <t>5956; 16035</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5685; 16402</t>
+          <t>5525; 16393</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>41958; 63891</t>
+          <t>42319; 65405</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66931; 94473</t>
+          <t>66518; 94477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34795; 55623</t>
+          <t>35953; 56109</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50974; 83798</t>
+          <t>49815; 83807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64880; 91946</t>
+          <t>64330; 91397</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83393; 112919</t>
+          <t>82133; 113032</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39466; 62714</t>
+          <t>40030; 61617</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>78411; 128649</t>
+          <t>78314; 134798</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>113794; 148427</t>
+          <t>114608; 148937</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>158541; 198974</t>
+          <t>158483; 198427</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79243; 111218</t>
+          <t>80399; 109931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>133324; 199520</t>
+          <t>136142; 202504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP08-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 14,13</t>
+          <t>7,04; 17,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 13,51</t>
+          <t>4,25; 13,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,77</t>
+          <t>3,97; 13,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 15,12</t>
+          <t>6,39; 16,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 17,89</t>
+          <t>5,73; 15,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,85</t>
+          <t>3,68; 13,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,46</t>
+          <t>2,94; 11,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 16,18</t>
+          <t>6,72; 16,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,86</t>
+          <t>7,63; 14,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,75</t>
+          <t>4,89; 11,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,66</t>
+          <t>4,67; 10,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 13,89</t>
+          <t>7,3; 14,37</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,82%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,56</t>
+          <t>5,66; 16,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,19</t>
+          <t>4,81; 14,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,59</t>
+          <t>4,27; 12,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 14,87</t>
+          <t>6,51; 18,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 16,43</t>
+          <t>4,76; 14,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 14,05</t>
+          <t>5,09; 14,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,45</t>
+          <t>0,61; 5,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 19,75</t>
+          <t>4,45; 14,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,43</t>
+          <t>6,5; 13,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,65</t>
+          <t>5,82; 12,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,89</t>
+          <t>3,14; 7,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,83</t>
+          <t>6,91; 14,74</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,5%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,73</t>
+          <t>8,95; 20,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,89</t>
+          <t>8,48; 21,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,12</t>
+          <t>3,89; 13,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,32</t>
+          <t>6,39; 21,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 19,61</t>
+          <t>2,07; 11,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 20,96</t>
+          <t>4,84; 15,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 13,92</t>
+          <t>1,98; 12,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 21,14</t>
+          <t>1,12; 11,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,45</t>
+          <t>7,11; 14,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,18</t>
+          <t>8,09; 16,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,88</t>
+          <t>3,72; 10,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 14,35</t>
+          <t>4,42; 13,44</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,61%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,05</t>
+          <t>7,1; 14,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 21,42</t>
+          <t>12,94; 21,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,82</t>
+          <t>3,1; 8,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 20,64</t>
+          <t>9,82; 18,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,61</t>
+          <t>5,64; 12,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 21,53</t>
+          <t>13,06; 21,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,12</t>
+          <t>5,09; 10,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 19,52</t>
+          <t>8,02; 15,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,9</t>
+          <t>7,07; 11,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,12</t>
+          <t>14,05; 20,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,59</t>
+          <t>4,93; 8,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,83</t>
+          <t>9,57; 15,82</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,4%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 13,88</t>
+          <t>8,89; 18,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 16,11</t>
+          <t>11,55; 22,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,31</t>
+          <t>3,95; 11,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,36</t>
+          <t>8,89; 36,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 18,24</t>
+          <t>4,66; 13,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,04</t>
+          <t>7,65; 16,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,99</t>
+          <t>6,49; 15,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 35,74</t>
+          <t>6,78; 16,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,34</t>
+          <t>8,02; 14,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 18,06</t>
+          <t>11,12; 17,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,54</t>
+          <t>6,17; 11,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 26,96</t>
+          <t>9,32; 24,54</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,15%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 13,18</t>
+          <t>5,64; 17,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 18,04</t>
+          <t>4,87; 15,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,0</t>
+          <t>4,94; 17,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 12,47</t>
+          <t>3,7; 16,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 18,35</t>
+          <t>2,98; 13,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 16,71</t>
+          <t>3,93; 17,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 18,82</t>
+          <t>1,24; 10,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 14,78</t>
+          <t>2,57; 13,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,56</t>
+          <t>5,65; 13,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,05</t>
+          <t>5,8; 14,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,51</t>
+          <t>4,47; 12,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,63</t>
+          <t>3,98; 12,03</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11,83%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,24</t>
+          <t>9,7; 13,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 13,94</t>
+          <t>11,44; 15,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,38</t>
+          <t>5,52; 8,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,76</t>
+          <t>10,4; 16,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,35</t>
+          <t>6,48; 10,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,77</t>
+          <t>9,96; 14,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,72</t>
+          <t>5,3; 8,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 18,04</t>
+          <t>7,68; 11,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,25</t>
+          <t>8,64; 11,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,23</t>
+          <t>11,3; 14,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,99</t>
+          <t>5,78; 8,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,42</t>
+          <t>9,44; 13,4</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11474</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7494</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7476</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12806</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>9789</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6802</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5358</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10623</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11474</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7494</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7476</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>23576</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5531; 14749</t>
+          <t>6870; 17402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3412; 12152</t>
+          <t>3814; 12551</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2756; 10546</t>
+          <t>3935; 13042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5992; 15800</t>
+          <t>7835; 19875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7203; 17454</t>
+          <t>5984; 16138</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3976; 12432</t>
+          <t>3312; 11797</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4042; 12346</t>
+          <t>2425; 9908</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8625; 22146</t>
+          <t>6915; 17325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15645; 30004</t>
+          <t>15396; 29431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9410; 21118</t>
+          <t>8793; 20933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7857; 19366</t>
+          <t>8485; 19941</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17725; 33521</t>
+          <t>16460; 32405</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8531</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10840</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7704</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8475</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2567</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8201</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8531</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19300</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4360; 13601</t>
+          <t>4869; 13797</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4403; 14165</t>
+          <t>4659; 13934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635; 5906</t>
+          <t>4817; 14089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4485; 14077</t>
+          <t>5954; 17011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4998; 14127</t>
+          <t>4158; 12894</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4569; 13598</t>
+          <t>4749; 13152</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4710; 14041</t>
+          <t>644; 5846</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6637; 18873</t>
+          <t>4295; 13700</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11061; 23289</t>
+          <t>11273; 23853</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11118; 24042</t>
+          <t>11054; 24149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6657; 17239</t>
+          <t>6866; 17194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12964; 28217</t>
+          <t>12990; 27702</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13871</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12145</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3842</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8182</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3323</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13871</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12145</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5744</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>9128</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1350; 7905</t>
+          <t>8891; 20250</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4415; 13687</t>
+          <t>7364; 18593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1255; 7493</t>
+          <t>2933; 10119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>796; 6336</t>
+          <t>3639; 12360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8590; 19481</t>
+          <t>1398; 7617</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7528; 18214</t>
+          <t>4168; 13152</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2916; 10500</t>
+          <t>1223; 7594</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3710; 13500</t>
+          <t>594; 6080</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11785; 25758</t>
+          <t>11854; 24484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14138; 28005</t>
+          <t>14002; 28208</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5349; 14937</t>
+          <t>5108; 14936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5634; 16542</t>
+          <t>4861; 14792</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20024</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39012</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10953</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27861</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>17409</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>34455</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16936</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25055</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39012</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10953</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56283</t>
+          <t>48099</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11742; 24187</t>
+          <t>14344; 28302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26299; 43988</t>
+          <t>29528; 49256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11326; 24105</t>
+          <t>6477; 17025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15907; 44987</t>
+          <t>19834; 37013</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13951; 27509</t>
+          <t>11316; 24136</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29557; 49105</t>
+          <t>26822; 44184</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6279; 16989</t>
+          <t>11325; 24273</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22768; 42617</t>
+          <t>14349; 28558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28617; 47927</t>
+          <t>28496; 46411</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62334; 87211</t>
+          <t>60892; 87149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20484; 37092</t>
+          <t>21270; 38085</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42477; 77772</t>
+          <t>36446; 60234</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23614</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9909</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22888</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8749</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17368</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>13749</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13020</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16181</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23614</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9909</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26496</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>35668</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4689; 14449</t>
+          <t>11317; 23258</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11697; 24033</t>
+          <t>16292; 31176</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8951; 20851</t>
+          <t>5621; 16471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8162; 19538</t>
+          <t>12976; 53553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10833; 23212</t>
+          <t>4852; 14416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16755; 31091</t>
+          <t>11411; 24627</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5190; 15648</t>
+          <t>8845; 20939</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13582; 57404</t>
+          <t>8045; 19680</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18227; 33179</t>
+          <t>18548; 33925</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32556; 52407</t>
+          <t>32280; 51272</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16201; 32158</t>
+          <t>17204; 31237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26509; 75492</t>
+          <t>24688; 64975</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7008</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7150</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5295</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2895</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7924</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7008</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7150</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10016</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2159; 9868</t>
+          <t>4085; 12571</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2153; 9728</t>
+          <t>3604; 11765</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>770; 6637</t>
+          <t>3351; 12102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1568; 8593</t>
+          <t>2524; 10978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4014; 13283</t>
+          <t>2234; 9859</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3646; 12372</t>
+          <t>2120; 9462</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3649; 12762</t>
+          <t>747; 6577</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2661; 10641</t>
+          <t>1809; 9846</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8247; 19969</t>
+          <t>8313; 19742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6954; 17981</t>
+          <t>7417; 18001</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5956; 16035</t>
+          <t>5724; 16269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5525; 16393</t>
+          <t>5514; 16675</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>78164</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>97578</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>49764</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>86705</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>52790</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>80218</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>44828</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>78164</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97578</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>49764</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>96639</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>160187</t>
+          <t>145787</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42319; 65405</t>
+          <t>66402; 92647</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66518; 94477</t>
+          <t>82001; 112574</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35953; 56109</t>
+          <t>39011; 62329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49815; 83807</t>
+          <t>71496; 114963</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64330; 91397</t>
+          <t>41397; 65264</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82133; 113032</t>
+          <t>67538; 95145</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40030; 61617</t>
+          <t>35501; 56726</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>78314; 134798</t>
+          <t>47681; 72552</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>114608; 148937</t>
+          <t>114391; 150190</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>158483; 198427</t>
+          <t>157505; 199804</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80399; 109931</t>
+          <t>79499; 110443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>136142; 202504</t>
+          <t>123415; 175165</t>
         </is>
       </c>
     </row>
